--- a/ducument/chonya_keep3.xlsx
+++ b/ducument/chonya_keep3.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -1068,7 +1068,7 @@
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.0666666666667" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.73333333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.6916666666667" style="2" customWidth="1"/>
